--- a/data_uji.xlsx
+++ b/data_uji.xlsx
@@ -1,24 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python_apps\apps_hafni\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3602731-2927-4B2E-B89F-53665280E097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="28680" yWindow="-10500" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="260">
   <si>
-    <t>nama_keluarga</t>
-  </si>
-  <si>
     <t>usia</t>
   </si>
   <si>
@@ -794,13 +797,16 @@
   </si>
   <si>
     <t>Tidak</t>
+  </si>
+  <si>
+    <t>nama</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -863,13 +869,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -907,7 +921,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -941,6 +955,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -975,9 +990,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1150,51 +1166,51 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J246"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>10</v>
       </c>
       <c r="B2">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D2">
         <v>1180412</v>
@@ -1206,59 +1222,59 @@
         <v>13.9</v>
       </c>
       <c r="G2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D3">
         <v>2254600</v>
       </c>
       <c r="E3">
-        <v>78.70999999999999</v>
+        <v>78.709999999999994</v>
       </c>
       <c r="F3">
         <v>10.68</v>
       </c>
       <c r="G3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J3" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D4">
         <v>4179299</v>
@@ -1270,27 +1286,27 @@
         <v>7.53</v>
       </c>
       <c r="G4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J4" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5">
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D5">
         <v>2051388</v>
@@ -1302,59 +1318,59 @@
         <v>10.62</v>
       </c>
       <c r="G5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J5" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6">
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D6">
         <v>1344346</v>
       </c>
       <c r="E6">
-        <v>71.23999999999999</v>
+        <v>71.239999999999995</v>
       </c>
       <c r="F6">
         <v>7.24</v>
       </c>
       <c r="G6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J6" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7">
         <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D7">
         <v>1354259</v>
@@ -1363,30 +1379,30 @@
         <v>67.47</v>
       </c>
       <c r="F7">
-        <v>17.49</v>
+        <v>17.489999999999998</v>
       </c>
       <c r="G7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J7" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8">
         <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D8">
         <v>2008390</v>
@@ -1398,27 +1414,27 @@
         <v>5.72</v>
       </c>
       <c r="G8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J8" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D9">
         <v>1161873</v>
@@ -1430,59 +1446,59 @@
         <v>11.52</v>
       </c>
       <c r="G9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J9" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D10">
         <v>4339967</v>
       </c>
       <c r="E10">
-        <v>71.93000000000001</v>
+        <v>71.930000000000007</v>
       </c>
       <c r="F10">
         <v>8.31</v>
       </c>
       <c r="G10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J10" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D11">
         <v>2695786</v>
@@ -1494,27 +1510,27 @@
         <v>5.58</v>
       </c>
       <c r="G11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J11" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12">
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D12">
         <v>4529934</v>
@@ -1526,27 +1542,27 @@
         <v>14.57</v>
       </c>
       <c r="G12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J12" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D13">
         <v>3003736</v>
@@ -1558,27 +1574,27 @@
         <v>3.46</v>
       </c>
       <c r="G13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J13" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14">
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D14">
         <v>1724078</v>
@@ -1590,59 +1606,59 @@
         <v>11.51</v>
       </c>
       <c r="G14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J14" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15">
         <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D15">
         <v>1002071</v>
       </c>
       <c r="E15">
-        <v>80.90000000000001</v>
+        <v>80.900000000000006</v>
       </c>
       <c r="F15">
         <v>10.18</v>
       </c>
       <c r="G15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H15" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J15" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16">
         <v>7</v>
       </c>
       <c r="C16" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D16">
         <v>1984190</v>
@@ -1654,27 +1670,27 @@
         <v>12.48</v>
       </c>
       <c r="G16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H16" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I16" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J16" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17">
         <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D17">
         <v>1838724</v>
@@ -1686,27 +1702,27 @@
         <v>10.46</v>
       </c>
       <c r="G17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J17" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18">
         <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D18">
         <v>3594325</v>
@@ -1718,59 +1734,59 @@
         <v>3.56</v>
       </c>
       <c r="G18" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H18" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I18" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J18" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19">
         <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D19">
         <v>1020980</v>
       </c>
       <c r="E19">
-        <v>80.65000000000001</v>
+        <v>80.650000000000006</v>
       </c>
       <c r="F19">
         <v>3.88</v>
       </c>
       <c r="G19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I19" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J19" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20">
         <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D20">
         <v>3496852</v>
@@ -1782,27 +1798,27 @@
         <v>17.55</v>
       </c>
       <c r="G20" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H20" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J20" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21">
         <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D21">
         <v>1860191</v>
@@ -1814,27 +1830,27 @@
         <v>17.37</v>
       </c>
       <c r="G21" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H21" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I21" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J21" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22">
         <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D22">
         <v>3838179</v>
@@ -1846,27 +1862,27 @@
         <v>12.7</v>
       </c>
       <c r="G22" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H22" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I22" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J22" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23">
         <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D23">
         <v>1213655</v>
@@ -1878,27 +1894,27 @@
         <v>8.06</v>
       </c>
       <c r="G23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I23" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J23" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24">
         <v>57</v>
       </c>
       <c r="C24" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D24">
         <v>4010756</v>
@@ -1910,27 +1926,27 @@
         <v>5.55</v>
       </c>
       <c r="G24" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H24" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I24" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J24" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25">
         <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D25">
         <v>3693548</v>
@@ -1942,59 +1958,59 @@
         <v>15.55</v>
       </c>
       <c r="G25" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H25" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I25" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J25" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26">
         <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D26">
         <v>1744707</v>
       </c>
       <c r="E26">
-        <v>86.06999999999999</v>
+        <v>86.07</v>
       </c>
       <c r="F26">
-        <v>8.380000000000001</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="G26" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I26" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J26" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27">
         <v>49</v>
       </c>
       <c r="C27" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D27">
         <v>4807914</v>
@@ -2006,27 +2022,27 @@
         <v>6.1</v>
       </c>
       <c r="G27" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H27" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I27" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J27" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28">
         <v>6</v>
       </c>
       <c r="C28" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D28">
         <v>1464331</v>
@@ -2035,30 +2051,30 @@
         <v>67.89</v>
       </c>
       <c r="F28">
-        <v>18.26</v>
+        <v>18.260000000000002</v>
       </c>
       <c r="G28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I28" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J28" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29">
         <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D29">
         <v>2967446</v>
@@ -2070,27 +2086,27 @@
         <v>5.73</v>
       </c>
       <c r="G29" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H29" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I29" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J29" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30">
         <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D30">
         <v>4931568</v>
@@ -2102,27 +2118,27 @@
         <v>13.06</v>
       </c>
       <c r="G30" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H30" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I30" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J30" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31">
         <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D31">
         <v>2812649</v>
@@ -2134,27 +2150,27 @@
         <v>5.33</v>
       </c>
       <c r="G31" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H31" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I31" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J31" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32">
         <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D32">
         <v>2266582</v>
@@ -2163,30 +2179,30 @@
         <v>71.98</v>
       </c>
       <c r="F32">
-        <v>4.19</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="G32" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H32" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I32" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J32" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B33">
         <v>11</v>
       </c>
       <c r="C33" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D33">
         <v>3395903</v>
@@ -2198,27 +2214,27 @@
         <v>5.12</v>
       </c>
       <c r="G33" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H33" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J33" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B34">
         <v>59</v>
       </c>
       <c r="C34" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D34">
         <v>3097998</v>
@@ -2230,27 +2246,27 @@
         <v>7.51</v>
       </c>
       <c r="G34" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H34" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I34" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J34" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B35">
         <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D35">
         <v>3986149</v>
@@ -2262,27 +2278,27 @@
         <v>14.68</v>
       </c>
       <c r="G35" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H35" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I35" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J35" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B36">
         <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D36">
         <v>1834051</v>
@@ -2294,59 +2310,59 @@
         <v>16.68</v>
       </c>
       <c r="G36" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H36" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I36" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J36" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B37">
         <v>10</v>
       </c>
       <c r="C37" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D37">
         <v>4315147</v>
       </c>
       <c r="E37">
-        <v>98.65000000000001</v>
+        <v>98.65</v>
       </c>
       <c r="F37">
         <v>11.01</v>
       </c>
       <c r="G37" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H37" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I37" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J37" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B38">
         <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D38">
         <v>4643827</v>
@@ -2358,27 +2374,27 @@
         <v>14.23</v>
       </c>
       <c r="G38" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H38" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I38" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J38" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39">
         <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D39">
         <v>4340535</v>
@@ -2390,27 +2406,27 @@
         <v>19.07</v>
       </c>
       <c r="G39" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I39" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J39" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B40">
         <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D40">
         <v>1171131</v>
@@ -2422,27 +2438,27 @@
         <v>6.79</v>
       </c>
       <c r="G40" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H40" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I40" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J40" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B41">
         <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D41">
         <v>4349988</v>
@@ -2454,59 +2470,59 @@
         <v>7.71</v>
       </c>
       <c r="G41" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H41" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I41" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J41" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B42">
         <v>41</v>
       </c>
       <c r="C42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D42">
         <v>4823227</v>
       </c>
       <c r="E42">
-        <v>91.70999999999999</v>
+        <v>91.71</v>
       </c>
       <c r="F42">
         <v>6.91</v>
       </c>
       <c r="G42" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H42" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I42" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J42" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B43">
         <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D43">
         <v>2169963</v>
@@ -2518,59 +2534,59 @@
         <v>11.23</v>
       </c>
       <c r="G43" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H43" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I43" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J43" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B44">
         <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D44">
         <v>2303126</v>
       </c>
       <c r="E44">
-        <v>77.09999999999999</v>
+        <v>77.099999999999994</v>
       </c>
       <c r="F44">
         <v>8.99</v>
       </c>
       <c r="G44" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H44" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I44" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J44" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B45">
         <v>24</v>
       </c>
       <c r="C45" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D45">
         <v>2775233</v>
@@ -2582,59 +2598,59 @@
         <v>3.57</v>
       </c>
       <c r="G45" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H45" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I45" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J45" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B46">
         <v>14</v>
       </c>
       <c r="C46" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D46">
         <v>1976521</v>
       </c>
       <c r="E46">
-        <v>84.29000000000001</v>
+        <v>84.29</v>
       </c>
       <c r="F46">
         <v>9.02</v>
       </c>
       <c r="G46" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H46" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I46" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J46" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B47">
         <v>37</v>
       </c>
       <c r="C47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D47">
         <v>2457945</v>
@@ -2646,27 +2662,27 @@
         <v>5.3</v>
       </c>
       <c r="G47" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H47" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I47" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J47" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B48">
         <v>7</v>
       </c>
       <c r="C48" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D48">
         <v>3855264</v>
@@ -2675,30 +2691,30 @@
         <v>62.73</v>
       </c>
       <c r="F48">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="G48" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H48" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I48" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J48" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B49">
         <v>14</v>
       </c>
       <c r="C49" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D49">
         <v>1948545</v>
@@ -2710,27 +2726,27 @@
         <v>10.61</v>
       </c>
       <c r="G49" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H49" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I49" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J49" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B50">
         <v>38</v>
       </c>
       <c r="C50" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D50">
         <v>4075294</v>
@@ -2742,27 +2758,27 @@
         <v>12.61</v>
       </c>
       <c r="G50" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H50" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I50" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J50" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B51">
         <v>28</v>
       </c>
       <c r="C51" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D51">
         <v>1207530</v>
@@ -2771,30 +2787,30 @@
         <v>93.88</v>
       </c>
       <c r="F51">
-        <v>16.92</v>
+        <v>16.920000000000002</v>
       </c>
       <c r="G51" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H51" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I51" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J51" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B52">
         <v>31</v>
       </c>
       <c r="C52" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D52">
         <v>3568808</v>
@@ -2806,27 +2822,27 @@
         <v>10.55</v>
       </c>
       <c r="G52" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H52" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I52" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J52" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B53">
         <v>35</v>
       </c>
       <c r="C53" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D53">
         <v>3685056</v>
@@ -2838,27 +2854,27 @@
         <v>15.51</v>
       </c>
       <c r="G53" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H53" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I53" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J53" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B54">
         <v>51</v>
       </c>
       <c r="C54" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D54">
         <v>2692261</v>
@@ -2870,27 +2886,27 @@
         <v>15.33</v>
       </c>
       <c r="G54" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H54" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I54" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J54" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B55">
         <v>43</v>
       </c>
       <c r="C55" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D55">
         <v>2357826</v>
@@ -2902,27 +2918,27 @@
         <v>16.32</v>
       </c>
       <c r="G55" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H55" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I55" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J55" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B56">
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D56">
         <v>1893293</v>
@@ -2934,91 +2950,91 @@
         <v>6.28</v>
       </c>
       <c r="G56" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H56" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I56" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J56" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B57">
         <v>53</v>
       </c>
       <c r="C57" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D57">
         <v>2042086</v>
       </c>
       <c r="E57">
-        <v>96.01000000000001</v>
+        <v>96.01</v>
       </c>
       <c r="F57">
         <v>5.86</v>
       </c>
       <c r="G57" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I57" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J57" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B58">
         <v>12</v>
       </c>
       <c r="C58" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D58">
         <v>4296196</v>
       </c>
       <c r="E58">
-        <v>91.20999999999999</v>
+        <v>91.21</v>
       </c>
       <c r="F58">
         <v>18.88</v>
       </c>
       <c r="G58" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H58" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I58" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J58" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B59">
         <v>54</v>
       </c>
       <c r="C59" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D59">
         <v>2582152</v>
@@ -3030,27 +3046,27 @@
         <v>7.03</v>
       </c>
       <c r="G59" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H59" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I59" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J59" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B60">
         <v>25</v>
       </c>
       <c r="C60" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D60">
         <v>2488407</v>
@@ -3062,59 +3078,59 @@
         <v>3.74</v>
       </c>
       <c r="G60" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H60" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I60" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J60" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B61">
         <v>42</v>
       </c>
       <c r="C61" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D61">
         <v>4329084</v>
       </c>
       <c r="E61">
-        <v>92.48999999999999</v>
+        <v>92.49</v>
       </c>
       <c r="F61">
         <v>19.21</v>
       </c>
       <c r="G61" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H61" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I61" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J61" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B62">
         <v>14</v>
       </c>
       <c r="C62" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D62">
         <v>3704930</v>
@@ -3126,27 +3142,27 @@
         <v>19.62</v>
       </c>
       <c r="G62" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H62" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I62" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J62" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B63">
         <v>58</v>
       </c>
       <c r="C63" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D63">
         <v>2845822</v>
@@ -3155,30 +3171,30 @@
         <v>54.42</v>
       </c>
       <c r="F63">
-        <v>9.619999999999999</v>
+        <v>9.6199999999999992</v>
       </c>
       <c r="G63" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H63" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I63" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J63" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B64">
         <v>49</v>
       </c>
       <c r="C64" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D64">
         <v>4760527</v>
@@ -3187,30 +3203,30 @@
         <v>86.44</v>
       </c>
       <c r="F64">
-        <v>8.130000000000001</v>
+        <v>8.1300000000000008</v>
       </c>
       <c r="G64" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H64" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I64" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J64" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B65">
         <v>17</v>
       </c>
       <c r="C65" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D65">
         <v>4459754</v>
@@ -3222,27 +3238,27 @@
         <v>15.28</v>
       </c>
       <c r="G65" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H65" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I65" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J65" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B66">
         <v>12</v>
       </c>
       <c r="C66" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D66">
         <v>2008921</v>
@@ -3254,27 +3270,27 @@
         <v>11.12</v>
       </c>
       <c r="G66" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H66" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I66" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J66" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B67">
         <v>48</v>
       </c>
       <c r="C67" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D67">
         <v>2174387</v>
@@ -3286,27 +3302,27 @@
         <v>10.19</v>
       </c>
       <c r="G67" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H67" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I67" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J67" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B68">
         <v>19</v>
       </c>
       <c r="C68" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D68">
         <v>3503833</v>
@@ -3318,27 +3334,27 @@
         <v>19.23</v>
       </c>
       <c r="G68" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H68" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I68" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J68" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B69">
         <v>27</v>
       </c>
       <c r="C69" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D69">
         <v>4375201</v>
@@ -3350,27 +3366,27 @@
         <v>8.26</v>
       </c>
       <c r="G69" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H69" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I69" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J69" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B70">
         <v>28</v>
       </c>
       <c r="C70" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D70">
         <v>3697616</v>
@@ -3382,59 +3398,59 @@
         <v>3.93</v>
       </c>
       <c r="G70" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H70" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I70" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J70" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B71">
         <v>17</v>
       </c>
       <c r="C71" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D71">
         <v>1598282</v>
       </c>
       <c r="E71">
-        <v>84.73999999999999</v>
+        <v>84.74</v>
       </c>
       <c r="F71">
-        <v>17.26</v>
+        <v>17.260000000000002</v>
       </c>
       <c r="G71" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H71" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I71" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J71" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B72">
         <v>33</v>
       </c>
       <c r="C72" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D72">
         <v>1583016</v>
@@ -3446,27 +3462,27 @@
         <v>15.98</v>
       </c>
       <c r="G72" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H72" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I72" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J72" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B73">
         <v>38</v>
       </c>
       <c r="C73" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D73">
         <v>4631088</v>
@@ -3478,27 +3494,27 @@
         <v>3.76</v>
       </c>
       <c r="G73" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H73" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I73" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J73" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B74">
         <v>6</v>
       </c>
       <c r="C74" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D74">
         <v>4532252</v>
@@ -3510,27 +3526,27 @@
         <v>16.95</v>
       </c>
       <c r="G74" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H74" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I74" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J74" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B75">
         <v>23</v>
       </c>
       <c r="C75" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D75">
         <v>2079089</v>
@@ -3542,27 +3558,27 @@
         <v>5.34</v>
       </c>
       <c r="G75" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H75" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I75" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J75" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B76">
         <v>54</v>
       </c>
       <c r="C76" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D76">
         <v>1981548</v>
@@ -3574,59 +3590,59 @@
         <v>14.06</v>
       </c>
       <c r="G76" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H76" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I76" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J76" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B77">
         <v>16</v>
       </c>
       <c r="C77" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D77">
         <v>4538319</v>
       </c>
       <c r="E77">
-        <v>85.79000000000001</v>
+        <v>85.79</v>
       </c>
       <c r="F77">
         <v>13.66</v>
       </c>
       <c r="G77" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H77" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I77" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J77" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B78">
         <v>56</v>
       </c>
       <c r="C78" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D78">
         <v>3525399</v>
@@ -3638,59 +3654,59 @@
         <v>9.06</v>
       </c>
       <c r="G78" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H78" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I78" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J78" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B79">
         <v>55</v>
       </c>
       <c r="C79" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D79">
         <v>2222645</v>
       </c>
       <c r="E79">
-        <v>75.65000000000001</v>
+        <v>75.650000000000006</v>
       </c>
       <c r="F79">
         <v>17.32</v>
       </c>
       <c r="G79" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H79" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I79" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J79" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B80">
         <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D80">
         <v>1812407</v>
@@ -3702,27 +3718,27 @@
         <v>4.83</v>
       </c>
       <c r="G80" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H80" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I80" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J80" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B81">
         <v>35</v>
       </c>
       <c r="C81" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D81">
         <v>2873702</v>
@@ -3734,27 +3750,27 @@
         <v>19.02</v>
       </c>
       <c r="G81" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H81" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I81" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J81" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B82">
         <v>22</v>
       </c>
       <c r="C82" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D82">
         <v>3822252</v>
@@ -3766,91 +3782,91 @@
         <v>5.9</v>
       </c>
       <c r="G82" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H82" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I82" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J82" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B83">
         <v>57</v>
       </c>
       <c r="C83" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D83">
         <v>2465616</v>
       </c>
       <c r="E83">
-        <v>87.18000000000001</v>
+        <v>87.18</v>
       </c>
       <c r="F83">
         <v>3.95</v>
       </c>
       <c r="G83" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H83" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I83" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J83" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B84">
         <v>32</v>
       </c>
       <c r="C84" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D84">
         <v>3706625</v>
       </c>
       <c r="E84">
-        <v>83.31999999999999</v>
+        <v>83.32</v>
       </c>
       <c r="F84">
         <v>17.89</v>
       </c>
       <c r="G84" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H84" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I84" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J84" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B85">
         <v>16</v>
       </c>
       <c r="C85" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D85">
         <v>1189939</v>
@@ -3862,59 +3878,59 @@
         <v>15.18</v>
       </c>
       <c r="G85" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H85" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I85" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J85" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B86">
         <v>24</v>
       </c>
       <c r="C86" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D86">
         <v>4077774</v>
       </c>
       <c r="E86">
-        <v>92.20999999999999</v>
+        <v>92.21</v>
       </c>
       <c r="F86">
         <v>17.61</v>
       </c>
       <c r="G86" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H86" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I86" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J86" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B87">
         <v>30</v>
       </c>
       <c r="C87" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D87">
         <v>1374611</v>
@@ -3926,27 +3942,27 @@
         <v>5.78</v>
       </c>
       <c r="G87" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H87" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I87" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J87" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B88">
         <v>10</v>
       </c>
       <c r="C88" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D88">
         <v>2426274</v>
@@ -3958,27 +3974,27 @@
         <v>19.82</v>
       </c>
       <c r="G88" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H88" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I88" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J88" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B89">
         <v>26</v>
       </c>
       <c r="C89" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D89">
         <v>1290136</v>
@@ -3990,91 +4006,91 @@
         <v>14.48</v>
       </c>
       <c r="G89" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H89" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I89" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J89" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B90">
         <v>57</v>
       </c>
       <c r="C90" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D90">
         <v>2518569</v>
       </c>
       <c r="E90">
-        <v>73.23999999999999</v>
+        <v>73.239999999999995</v>
       </c>
       <c r="F90">
         <v>16.32</v>
       </c>
       <c r="G90" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H90" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I90" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J90" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B91">
         <v>12</v>
       </c>
       <c r="C91" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D91">
         <v>1103753</v>
       </c>
       <c r="E91">
-        <v>70.18000000000001</v>
+        <v>70.180000000000007</v>
       </c>
       <c r="F91">
-        <v>16.69</v>
+        <v>16.690000000000001</v>
       </c>
       <c r="G91" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H91" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I91" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J91" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B92">
         <v>39</v>
       </c>
       <c r="C92" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D92">
         <v>2725513</v>
@@ -4086,27 +4102,27 @@
         <v>7.13</v>
       </c>
       <c r="G92" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H92" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I92" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J92" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B93">
         <v>49</v>
       </c>
       <c r="C93" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D93">
         <v>3349162</v>
@@ -4115,30 +4131,30 @@
         <v>55.63</v>
       </c>
       <c r="F93">
-        <v>16.76</v>
+        <v>16.760000000000002</v>
       </c>
       <c r="G93" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H93" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I93" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J93" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B94">
         <v>31</v>
       </c>
       <c r="C94" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D94">
         <v>3865312</v>
@@ -4147,30 +4163,30 @@
         <v>95.25</v>
       </c>
       <c r="F94">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="G94" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H94" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I94" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J94" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B95">
         <v>50</v>
       </c>
       <c r="C95" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D95">
         <v>1915322</v>
@@ -4182,27 +4198,27 @@
         <v>4.09</v>
       </c>
       <c r="G95" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H95" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I95" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J95" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B96">
         <v>54</v>
       </c>
       <c r="C96" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D96">
         <v>2560641</v>
@@ -4214,27 +4230,27 @@
         <v>8.57</v>
       </c>
       <c r="G96" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H96" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I96" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J96" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B97">
         <v>22</v>
       </c>
       <c r="C97" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D97">
         <v>1012764</v>
@@ -4246,27 +4262,27 @@
         <v>3.38</v>
       </c>
       <c r="G97" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H97" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I97" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J97" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B98">
         <v>37</v>
       </c>
       <c r="C98" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D98">
         <v>2806301</v>
@@ -4278,27 +4294,27 @@
         <v>16.97</v>
       </c>
       <c r="G98" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H98" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I98" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J98" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B99">
         <v>23</v>
       </c>
       <c r="C99" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D99">
         <v>4353477</v>
@@ -4310,27 +4326,27 @@
         <v>17.36</v>
       </c>
       <c r="G99" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H99" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I99" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J99" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B100">
         <v>29</v>
       </c>
       <c r="C100" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D100">
         <v>2374355</v>
@@ -4342,27 +4358,27 @@
         <v>4.28</v>
       </c>
       <c r="G100" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H100" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I100" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J100" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B101">
         <v>16</v>
       </c>
       <c r="C101" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D101">
         <v>4870851</v>
@@ -4374,27 +4390,27 @@
         <v>19.66</v>
       </c>
       <c r="G101" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H101" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I101" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J101" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B102">
         <v>11</v>
       </c>
       <c r="C102" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D102">
         <v>1438337</v>
@@ -4406,27 +4422,27 @@
         <v>10.53</v>
       </c>
       <c r="G102" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H102" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I102" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J102" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B103">
         <v>58</v>
       </c>
       <c r="C103" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D103">
         <v>3127383</v>
@@ -4435,30 +4451,30 @@
         <v>53.37</v>
       </c>
       <c r="F103">
-        <v>16.17</v>
+        <v>16.170000000000002</v>
       </c>
       <c r="G103" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H103" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I103" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J103" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B104">
         <v>25</v>
       </c>
       <c r="C104" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D104">
         <v>1787231</v>
@@ -4470,27 +4486,27 @@
         <v>10.01</v>
       </c>
       <c r="G104" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H104" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I104" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J104" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B105">
         <v>58</v>
       </c>
       <c r="C105" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D105">
         <v>3876744</v>
@@ -4502,59 +4518,59 @@
         <v>18.53</v>
       </c>
       <c r="G105" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H105" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I105" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J105" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B106">
         <v>48</v>
       </c>
       <c r="C106" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D106">
         <v>3757787</v>
       </c>
       <c r="E106">
-        <v>71.43000000000001</v>
+        <v>71.430000000000007</v>
       </c>
       <c r="F106">
         <v>13.18</v>
       </c>
       <c r="G106" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H106" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I106" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J106" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B107">
         <v>30</v>
       </c>
       <c r="C107" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D107">
         <v>1589220</v>
@@ -4566,59 +4582,59 @@
         <v>5.19</v>
       </c>
       <c r="G107" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H107" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I107" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J107" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B108">
         <v>19</v>
       </c>
       <c r="C108" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D108">
         <v>2694367</v>
       </c>
       <c r="E108">
-        <v>70.95999999999999</v>
+        <v>70.959999999999994</v>
       </c>
       <c r="F108">
         <v>15.32</v>
       </c>
       <c r="G108" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H108" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I108" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J108" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B109">
         <v>7</v>
       </c>
       <c r="C109" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D109">
         <v>3282532</v>
@@ -4630,27 +4646,27 @@
         <v>3.79</v>
       </c>
       <c r="G109" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H109" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I109" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J109" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B110">
         <v>38</v>
       </c>
       <c r="C110" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D110">
         <v>1240358</v>
@@ -4662,27 +4678,27 @@
         <v>3.46</v>
       </c>
       <c r="G110" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H110" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I110" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J110" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B111">
         <v>21</v>
       </c>
       <c r="C111" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D111">
         <v>1087394</v>
@@ -4694,27 +4710,27 @@
         <v>13.74</v>
       </c>
       <c r="G111" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H111" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I111" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J111" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B112">
         <v>50</v>
       </c>
       <c r="C112" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D112">
         <v>3742760</v>
@@ -4726,27 +4742,27 @@
         <v>10.65</v>
       </c>
       <c r="G112" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H112" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I112" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J112" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B113">
         <v>56</v>
       </c>
       <c r="C113" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D113">
         <v>4334754</v>
@@ -4758,59 +4774,59 @@
         <v>15.73</v>
       </c>
       <c r="G113" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H113" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I113" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J113" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B114">
         <v>21</v>
       </c>
       <c r="C114" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D114">
         <v>4990475</v>
       </c>
       <c r="E114">
-        <v>77.29000000000001</v>
+        <v>77.290000000000006</v>
       </c>
       <c r="F114">
-        <v>4.64</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="G114" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H114" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I114" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J114" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B115">
         <v>44</v>
       </c>
       <c r="C115" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D115">
         <v>3872577</v>
@@ -4822,59 +4838,59 @@
         <v>7.02</v>
       </c>
       <c r="G115" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H115" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I115" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J115" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B116">
         <v>32</v>
       </c>
       <c r="C116" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D116">
         <v>3279758</v>
       </c>
       <c r="E116">
-        <v>86.56999999999999</v>
+        <v>86.57</v>
       </c>
       <c r="F116">
         <v>19.84</v>
       </c>
       <c r="G116" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H116" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I116" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J116" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B117">
         <v>56</v>
       </c>
       <c r="C117" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D117">
         <v>1879406</v>
@@ -4886,27 +4902,27 @@
         <v>14.64</v>
       </c>
       <c r="G117" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H117" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I117" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J117" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B118">
         <v>22</v>
       </c>
       <c r="C118" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D118">
         <v>4530396</v>
@@ -4915,62 +4931,62 @@
         <v>61.87</v>
       </c>
       <c r="F118">
-        <v>9.279999999999999</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="G118" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H118" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I118" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J118" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B119">
         <v>32</v>
       </c>
       <c r="C119" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D119">
         <v>3767807</v>
       </c>
       <c r="E119">
-        <v>87.98999999999999</v>
+        <v>87.99</v>
       </c>
       <c r="F119">
-        <v>8.039999999999999</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="G119" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H119" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I119" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J119" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B120">
         <v>33</v>
       </c>
       <c r="C120" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D120">
         <v>2415642</v>
@@ -4982,27 +4998,27 @@
         <v>10.06</v>
       </c>
       <c r="G120" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H120" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I120" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J120" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B121">
         <v>29</v>
       </c>
       <c r="C121" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D121">
         <v>4523021</v>
@@ -5014,27 +5030,27 @@
         <v>16.91</v>
       </c>
       <c r="G121" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H121" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I121" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J121" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B122">
         <v>23</v>
       </c>
       <c r="C122" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D122">
         <v>2665230</v>
@@ -5046,27 +5062,27 @@
         <v>6.57</v>
       </c>
       <c r="G122" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H122" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I122" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J122" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B123">
         <v>47</v>
       </c>
       <c r="C123" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D123">
         <v>1000730</v>
@@ -5078,59 +5094,59 @@
         <v>7.36</v>
       </c>
       <c r="G123" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H123" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I123" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J123" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B124">
         <v>50</v>
       </c>
       <c r="C124" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D124">
         <v>4844099</v>
       </c>
       <c r="E124">
-        <v>90.95999999999999</v>
+        <v>90.96</v>
       </c>
       <c r="F124">
-        <v>17.92</v>
+        <v>17.920000000000002</v>
       </c>
       <c r="G124" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H124" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I124" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J124" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B125">
         <v>11</v>
       </c>
       <c r="C125" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D125">
         <v>1620300</v>
@@ -5142,27 +5158,27 @@
         <v>15.63</v>
       </c>
       <c r="G125" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H125" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I125" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J125" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B126">
         <v>25</v>
       </c>
       <c r="C126" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D126">
         <v>1599628</v>
@@ -5171,30 +5187,30 @@
         <v>65.59</v>
       </c>
       <c r="F126">
-        <v>17.81</v>
+        <v>17.809999999999999</v>
       </c>
       <c r="G126" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H126" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I126" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J126" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B127">
         <v>13</v>
       </c>
       <c r="C127" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D127">
         <v>1715078</v>
@@ -5206,27 +5222,27 @@
         <v>10.97</v>
       </c>
       <c r="G127" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H127" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I127" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J127" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B128">
         <v>57</v>
       </c>
       <c r="C128" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D128">
         <v>3691392</v>
@@ -5238,27 +5254,27 @@
         <v>9.65</v>
       </c>
       <c r="G128" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H128" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I128" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J128" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B129">
         <v>59</v>
       </c>
       <c r="C129" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D129">
         <v>3070219</v>
@@ -5270,59 +5286,59 @@
         <v>8.9</v>
       </c>
       <c r="G129" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H129" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I129" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J129" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B130">
         <v>41</v>
       </c>
       <c r="C130" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D130">
         <v>2486710</v>
       </c>
       <c r="E130">
-        <v>69.70999999999999</v>
+        <v>69.709999999999994</v>
       </c>
       <c r="F130">
         <v>4.37</v>
       </c>
       <c r="G130" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H130" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I130" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J130" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B131">
         <v>45</v>
       </c>
       <c r="C131" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D131">
         <v>2836702</v>
@@ -5334,59 +5350,59 @@
         <v>15.98</v>
       </c>
       <c r="G131" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H131" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I131" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J131" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B132">
         <v>21</v>
       </c>
       <c r="C132" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D132">
         <v>1704558</v>
       </c>
       <c r="E132">
-        <v>69.84999999999999</v>
+        <v>69.849999999999994</v>
       </c>
       <c r="F132">
-        <v>17.49</v>
+        <v>17.489999999999998</v>
       </c>
       <c r="G132" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H132" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I132" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J132" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B133">
         <v>39</v>
       </c>
       <c r="C133" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D133">
         <v>1659293</v>
@@ -5398,59 +5414,59 @@
         <v>15.85</v>
       </c>
       <c r="G133" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H133" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I133" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J133" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B134">
         <v>36</v>
       </c>
       <c r="C134" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D134">
         <v>3846357</v>
       </c>
       <c r="E134">
-        <v>66.29000000000001</v>
+        <v>66.290000000000006</v>
       </c>
       <c r="F134">
         <v>4.05</v>
       </c>
       <c r="G134" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H134" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I134" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J134" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B135">
         <v>19</v>
       </c>
       <c r="C135" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D135">
         <v>1837297</v>
@@ -5462,91 +5478,91 @@
         <v>17.18</v>
       </c>
       <c r="G135" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H135" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I135" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J135" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B136">
         <v>10</v>
       </c>
       <c r="C136" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D136">
         <v>2302549</v>
       </c>
       <c r="E136">
-        <v>74.23999999999999</v>
+        <v>74.239999999999995</v>
       </c>
       <c r="F136">
         <v>5.26</v>
       </c>
       <c r="G136" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H136" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I136" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J136" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B137">
         <v>8</v>
       </c>
       <c r="C137" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D137">
         <v>2663719</v>
       </c>
       <c r="E137">
-        <v>88.31999999999999</v>
+        <v>88.32</v>
       </c>
       <c r="F137">
         <v>5.88</v>
       </c>
       <c r="G137" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H137" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I137" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J137" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B138">
         <v>29</v>
       </c>
       <c r="C138" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D138">
         <v>2353840</v>
@@ -5558,27 +5574,27 @@
         <v>5.17</v>
       </c>
       <c r="G138" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H138" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I138" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J138" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B139">
         <v>31</v>
       </c>
       <c r="C139" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D139">
         <v>2265595</v>
@@ -5590,27 +5606,27 @@
         <v>15.65</v>
       </c>
       <c r="G139" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H139" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I139" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J139" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B140">
         <v>51</v>
       </c>
       <c r="C140" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D140">
         <v>3616649</v>
@@ -5622,59 +5638,59 @@
         <v>15.92</v>
       </c>
       <c r="G140" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H140" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I140" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J140" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B141">
         <v>15</v>
       </c>
       <c r="C141" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D141">
         <v>3987923</v>
       </c>
       <c r="E141">
-        <v>81.95999999999999</v>
+        <v>81.96</v>
       </c>
       <c r="F141">
         <v>6.4</v>
       </c>
       <c r="G141" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H141" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I141" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J141" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B142">
         <v>50</v>
       </c>
       <c r="C142" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D142">
         <v>2743919</v>
@@ -5683,30 +5699,30 @@
         <v>63.69</v>
       </c>
       <c r="F142">
-        <v>18.15</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="G142" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H142" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I142" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J142" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B143">
         <v>52</v>
       </c>
       <c r="C143" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D143">
         <v>2403190</v>
@@ -5718,27 +5734,27 @@
         <v>13.96</v>
       </c>
       <c r="G143" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H143" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I143" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J143" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B144">
         <v>40</v>
       </c>
       <c r="C144" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D144">
         <v>4379098</v>
@@ -5747,30 +5763,30 @@
         <v>78.02</v>
       </c>
       <c r="F144">
-        <v>8.720000000000001</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="G144" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H144" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I144" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J144" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B145">
         <v>54</v>
       </c>
       <c r="C145" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D145">
         <v>2675904</v>
@@ -5779,30 +5795,30 @@
         <v>50.56</v>
       </c>
       <c r="F145">
-        <v>9.140000000000001</v>
+        <v>9.14</v>
       </c>
       <c r="G145" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H145" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I145" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J145" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B146">
         <v>40</v>
       </c>
       <c r="C146" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D146">
         <v>2436075</v>
@@ -5814,59 +5830,59 @@
         <v>7.26</v>
       </c>
       <c r="G146" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H146" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I146" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J146" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B147">
         <v>41</v>
       </c>
       <c r="C147" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D147">
         <v>3499831</v>
       </c>
       <c r="E147">
-        <v>64.70999999999999</v>
+        <v>64.709999999999994</v>
       </c>
       <c r="F147">
         <v>5.17</v>
       </c>
       <c r="G147" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H147" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I147" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J147" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B148">
         <v>51</v>
       </c>
       <c r="C148" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D148">
         <v>4554317</v>
@@ -5878,59 +5894,59 @@
         <v>12.46</v>
       </c>
       <c r="G148" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H148" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I148" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J148" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B149">
         <v>15</v>
       </c>
       <c r="C149" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D149">
         <v>4739863</v>
       </c>
       <c r="E149">
-        <v>87.70999999999999</v>
+        <v>87.71</v>
       </c>
       <c r="F149">
         <v>19.78</v>
       </c>
       <c r="G149" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H149" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I149" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J149" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B150">
         <v>12</v>
       </c>
       <c r="C150" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D150">
         <v>2858662</v>
@@ -5942,27 +5958,27 @@
         <v>7.14</v>
       </c>
       <c r="G150" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H150" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I150" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J150" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B151">
         <v>15</v>
       </c>
       <c r="C151" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D151">
         <v>4831098</v>
@@ -5974,27 +5990,27 @@
         <v>9.52</v>
       </c>
       <c r="G151" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H151" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I151" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J151" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B152">
         <v>41</v>
       </c>
       <c r="C152" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D152">
         <v>2872694</v>
@@ -6006,27 +6022,27 @@
         <v>18.7</v>
       </c>
       <c r="G152" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H152" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I152" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J152" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B153">
         <v>47</v>
       </c>
       <c r="C153" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D153">
         <v>3098675</v>
@@ -6035,62 +6051,62 @@
         <v>61.19</v>
       </c>
       <c r="F153">
-        <v>16.42</v>
+        <v>16.420000000000002</v>
       </c>
       <c r="G153" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H153" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I153" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J153" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B154">
         <v>47</v>
       </c>
       <c r="C154" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D154">
         <v>1858217</v>
       </c>
       <c r="E154">
-        <v>78.54000000000001</v>
+        <v>78.540000000000006</v>
       </c>
       <c r="F154">
         <v>19.05</v>
       </c>
       <c r="G154" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H154" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I154" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J154" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B155">
         <v>55</v>
       </c>
       <c r="C155" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D155">
         <v>4850141</v>
@@ -6102,59 +6118,59 @@
         <v>16.86</v>
       </c>
       <c r="G155" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H155" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I155" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J155" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B156">
         <v>31</v>
       </c>
       <c r="C156" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D156">
         <v>4036302</v>
       </c>
       <c r="E156">
-        <v>92.70999999999999</v>
+        <v>92.71</v>
       </c>
       <c r="F156">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="G156" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H156" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I156" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J156" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B157">
         <v>23</v>
       </c>
       <c r="C157" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D157">
         <v>2418537</v>
@@ -6166,27 +6182,27 @@
         <v>8.27</v>
       </c>
       <c r="G157" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H157" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I157" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J157" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B158">
         <v>29</v>
       </c>
       <c r="C158" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D158">
         <v>3228884</v>
@@ -6198,59 +6214,59 @@
         <v>10.75</v>
       </c>
       <c r="G158" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H158" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I158" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J158" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B159">
         <v>30</v>
       </c>
       <c r="C159" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D159">
         <v>2115682</v>
       </c>
       <c r="E159">
-        <v>69.43000000000001</v>
+        <v>69.430000000000007</v>
       </c>
       <c r="F159">
         <v>8.59</v>
       </c>
       <c r="G159" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H159" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I159" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J159" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B160">
         <v>25</v>
       </c>
       <c r="C160" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D160">
         <v>2974539</v>
@@ -6262,27 +6278,27 @@
         <v>12.92</v>
       </c>
       <c r="G160" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H160" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I160" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J160" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B161">
         <v>14</v>
       </c>
       <c r="C161" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D161">
         <v>3981680</v>
@@ -6294,27 +6310,27 @@
         <v>15.61</v>
       </c>
       <c r="G161" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H161" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I161" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J161" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B162">
         <v>50</v>
       </c>
       <c r="C162" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D162">
         <v>1281270</v>
@@ -6323,30 +6339,30 @@
         <v>65.88</v>
       </c>
       <c r="F162">
-        <v>18.83</v>
+        <v>18.829999999999998</v>
       </c>
       <c r="G162" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H162" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I162" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J162" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B163">
         <v>37</v>
       </c>
       <c r="C163" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D163">
         <v>2971072</v>
@@ -6355,62 +6371,62 @@
         <v>71.75</v>
       </c>
       <c r="F163">
-        <v>17.76</v>
+        <v>17.760000000000002</v>
       </c>
       <c r="G163" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H163" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I163" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J163" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B164">
         <v>56</v>
       </c>
       <c r="C164" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D164">
         <v>2925849</v>
       </c>
       <c r="E164">
-        <v>75.18000000000001</v>
+        <v>75.180000000000007</v>
       </c>
       <c r="F164">
-        <v>8.699999999999999</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="G164" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H164" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I164" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J164" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="165" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B165">
         <v>55</v>
       </c>
       <c r="C165" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D165">
         <v>4813130</v>
@@ -6422,59 +6438,59 @@
         <v>16.22</v>
       </c>
       <c r="G165" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H165" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I165" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J165" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="166" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B166">
         <v>16</v>
       </c>
       <c r="C166" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D166">
         <v>4534829</v>
       </c>
       <c r="E166">
-        <v>88.26000000000001</v>
+        <v>88.26</v>
       </c>
       <c r="F166">
         <v>5.88</v>
       </c>
       <c r="G166" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H166" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I166" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J166" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B167">
         <v>48</v>
       </c>
       <c r="C167" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D167">
         <v>1590662</v>
@@ -6486,27 +6502,27 @@
         <v>7.69</v>
       </c>
       <c r="G167" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H167" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I167" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J167" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="168" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B168">
         <v>7</v>
       </c>
       <c r="C168" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D168">
         <v>3877707</v>
@@ -6518,27 +6534,27 @@
         <v>12.52</v>
       </c>
       <c r="G168" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H168" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I168" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J168" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="169" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B169">
         <v>12</v>
       </c>
       <c r="C169" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D169">
         <v>1187512</v>
@@ -6550,27 +6566,27 @@
         <v>6.54</v>
       </c>
       <c r="G169" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H169" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I169" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J169" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="170" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B170">
         <v>15</v>
       </c>
       <c r="C170" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D170">
         <v>4285682</v>
@@ -6582,27 +6598,27 @@
         <v>18.03</v>
       </c>
       <c r="G170" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H170" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I170" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J170" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="171" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B171">
         <v>8</v>
       </c>
       <c r="C171" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D171">
         <v>4462905</v>
@@ -6614,27 +6630,27 @@
         <v>17.39</v>
       </c>
       <c r="G171" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H171" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I171" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J171" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="172" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B172">
         <v>37</v>
       </c>
       <c r="C172" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D172">
         <v>2227655</v>
@@ -6646,27 +6662,27 @@
         <v>6.78</v>
       </c>
       <c r="G172" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H172" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I172" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J172" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B173">
         <v>25</v>
       </c>
       <c r="C173" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D173">
         <v>2538179</v>
@@ -6678,59 +6694,59 @@
         <v>3.13</v>
       </c>
       <c r="G173" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H173" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I173" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J173" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="174" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B174">
         <v>50</v>
       </c>
       <c r="C174" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D174">
         <v>4040570</v>
       </c>
       <c r="E174">
-        <v>65.93000000000001</v>
+        <v>65.930000000000007</v>
       </c>
       <c r="F174">
         <v>8.4</v>
       </c>
       <c r="G174" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H174" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I174" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J174" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="175" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B175">
         <v>51</v>
       </c>
       <c r="C175" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D175">
         <v>3944364</v>
@@ -6742,27 +6758,27 @@
         <v>4</v>
       </c>
       <c r="G175" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H175" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I175" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J175" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="176" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B176">
         <v>30</v>
       </c>
       <c r="C176" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D176">
         <v>4445830</v>
@@ -6774,27 +6790,27 @@
         <v>10.75</v>
       </c>
       <c r="G176" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H176" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I176" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J176" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="177" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B177">
         <v>18</v>
       </c>
       <c r="C177" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D177">
         <v>4037767</v>
@@ -6806,27 +6822,27 @@
         <v>3.44</v>
       </c>
       <c r="G177" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H177" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I177" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J177" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="178" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B178">
         <v>34</v>
       </c>
       <c r="C178" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D178">
         <v>2496028</v>
@@ -6838,27 +6854,27 @@
         <v>15.82</v>
       </c>
       <c r="G178" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H178" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I178" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J178" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="179" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B179">
         <v>45</v>
       </c>
       <c r="C179" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D179">
         <v>3445067</v>
@@ -6867,30 +6883,30 @@
         <v>53.14</v>
       </c>
       <c r="F179">
-        <v>4.02</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="G179" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H179" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I179" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J179" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="180" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B180">
         <v>52</v>
       </c>
       <c r="C180" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D180">
         <v>4462458</v>
@@ -6899,62 +6915,62 @@
         <v>63.71</v>
       </c>
       <c r="F180">
-        <v>18.15</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="G180" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H180" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I180" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J180" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="181" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B181">
         <v>30</v>
       </c>
       <c r="C181" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D181">
         <v>1182597</v>
       </c>
       <c r="E181">
-        <v>95.18000000000001</v>
+        <v>95.18</v>
       </c>
       <c r="F181">
         <v>12.55</v>
       </c>
       <c r="G181" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H181" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I181" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J181" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="182" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B182">
         <v>12</v>
       </c>
       <c r="C182" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D182">
         <v>1763044</v>
@@ -6966,27 +6982,27 @@
         <v>17.3</v>
       </c>
       <c r="G182" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H182" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I182" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J182" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="183" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B183">
         <v>10</v>
       </c>
       <c r="C183" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D183">
         <v>2314740</v>
@@ -6998,27 +7014,27 @@
         <v>7.93</v>
       </c>
       <c r="G183" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H183" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I183" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J183" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="184" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B184">
         <v>52</v>
       </c>
       <c r="C184" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D184">
         <v>2389965</v>
@@ -7027,62 +7043,62 @@
         <v>77.53</v>
       </c>
       <c r="F184">
-        <v>16.01</v>
+        <v>16.010000000000002</v>
       </c>
       <c r="G184" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H184" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I184" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J184" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="185" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B185">
         <v>29</v>
       </c>
       <c r="C185" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D185">
         <v>3760540</v>
       </c>
       <c r="E185">
-        <v>84.34999999999999</v>
+        <v>84.35</v>
       </c>
       <c r="F185">
         <v>13.08</v>
       </c>
       <c r="G185" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H185" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I185" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J185" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="186" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B186">
         <v>18</v>
       </c>
       <c r="C186" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D186">
         <v>3676542</v>
@@ -7094,59 +7110,59 @@
         <v>19.02</v>
       </c>
       <c r="G186" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H186" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I186" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J186" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="187" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B187">
         <v>28</v>
       </c>
       <c r="C187" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D187">
         <v>4915025</v>
       </c>
       <c r="E187">
-        <v>92.15000000000001</v>
+        <v>92.15</v>
       </c>
       <c r="F187">
-        <v>16.31</v>
+        <v>16.309999999999999</v>
       </c>
       <c r="G187" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H187" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I187" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J187" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="188" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B188">
         <v>44</v>
       </c>
       <c r="C188" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D188">
         <v>3896939</v>
@@ -7155,30 +7171,30 @@
         <v>63.85</v>
       </c>
       <c r="F188">
-        <v>17.4</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="G188" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H188" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I188" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J188" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="189" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B189">
         <v>21</v>
       </c>
       <c r="C189" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D189">
         <v>1714874</v>
@@ -7187,62 +7203,62 @@
         <v>81.83</v>
       </c>
       <c r="F189">
-        <v>4.06</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="G189" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H189" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I189" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J189" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="190" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B190">
         <v>18</v>
       </c>
       <c r="C190" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D190">
         <v>3652742</v>
       </c>
       <c r="E190">
-        <v>82.90000000000001</v>
+        <v>82.9</v>
       </c>
       <c r="F190">
         <v>11.16</v>
       </c>
       <c r="G190" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H190" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I190" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J190" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="191" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B191">
         <v>46</v>
       </c>
       <c r="C191" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D191">
         <v>4950555</v>
@@ -7254,27 +7270,27 @@
         <v>11.38</v>
       </c>
       <c r="G191" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H191" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I191" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J191" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="192" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B192">
         <v>12</v>
       </c>
       <c r="C192" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D192">
         <v>3471692</v>
@@ -7286,59 +7302,59 @@
         <v>14.07</v>
       </c>
       <c r="G192" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H192" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I192" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J192" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="193" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B193">
         <v>39</v>
       </c>
       <c r="C193" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D193">
         <v>1859950</v>
       </c>
       <c r="E193">
-        <v>86.76000000000001</v>
+        <v>86.76</v>
       </c>
       <c r="F193">
         <v>16.22</v>
       </c>
       <c r="G193" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H193" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I193" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J193" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="194" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B194">
         <v>13</v>
       </c>
       <c r="C194" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D194">
         <v>2002497</v>
@@ -7350,27 +7366,27 @@
         <v>11.36</v>
       </c>
       <c r="G194" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H194" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I194" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J194" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="195" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B195">
         <v>59</v>
       </c>
       <c r="C195" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D195">
         <v>3233880</v>
@@ -7382,27 +7398,27 @@
         <v>12.35</v>
       </c>
       <c r="G195" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H195" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I195" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J195" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="196" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B196">
         <v>40</v>
       </c>
       <c r="C196" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D196">
         <v>2500833</v>
@@ -7414,91 +7430,91 @@
         <v>12.54</v>
       </c>
       <c r="G196" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H196" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I196" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J196" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="197" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B197">
         <v>57</v>
       </c>
       <c r="C197" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D197">
         <v>4134045</v>
       </c>
       <c r="E197">
-        <v>77.90000000000001</v>
+        <v>77.900000000000006</v>
       </c>
       <c r="F197">
         <v>17.77</v>
       </c>
       <c r="G197" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H197" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I197" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J197" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="198" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B198">
         <v>7</v>
       </c>
       <c r="C198" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D198">
         <v>4574118</v>
       </c>
       <c r="E198">
-        <v>99.79000000000001</v>
+        <v>99.79</v>
       </c>
       <c r="F198">
         <v>3.77</v>
       </c>
       <c r="G198" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H198" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I198" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J198" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="199" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B199">
         <v>17</v>
       </c>
       <c r="C199" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D199">
         <v>1129729</v>
@@ -7510,27 +7526,27 @@
         <v>3.49</v>
       </c>
       <c r="G199" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H199" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I199" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J199" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="200" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B200">
         <v>50</v>
       </c>
       <c r="C200" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D200">
         <v>2209987</v>
@@ -7542,27 +7558,27 @@
         <v>17.97</v>
       </c>
       <c r="G200" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H200" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I200" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J200" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="201" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B201">
         <v>33</v>
       </c>
       <c r="C201" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D201">
         <v>3003821</v>
@@ -7571,30 +7587,30 @@
         <v>54.61</v>
       </c>
       <c r="F201">
-        <v>18.81</v>
+        <v>18.809999999999999</v>
       </c>
       <c r="G201" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H201" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I201" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J201" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="202" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B202">
         <v>25</v>
       </c>
       <c r="C202" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D202">
         <v>3562977</v>
@@ -7606,27 +7622,27 @@
         <v>5.98</v>
       </c>
       <c r="G202" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H202" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I202" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J202" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="203" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B203">
         <v>35</v>
       </c>
       <c r="C203" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D203">
         <v>4682629</v>
@@ -7635,30 +7651,30 @@
         <v>60.65</v>
       </c>
       <c r="F203">
-        <v>10.12</v>
+        <v>10.119999999999999</v>
       </c>
       <c r="G203" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H203" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I203" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J203" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="204" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B204">
         <v>50</v>
       </c>
       <c r="C204" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D204">
         <v>4010901</v>
@@ -7667,30 +7683,30 @@
         <v>83.97</v>
       </c>
       <c r="F204">
-        <v>18.81</v>
+        <v>18.809999999999999</v>
       </c>
       <c r="G204" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H204" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I204" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J204" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="205" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B205">
         <v>41</v>
       </c>
       <c r="C205" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D205">
         <v>2513210</v>
@@ -7702,27 +7718,27 @@
         <v>16.95</v>
       </c>
       <c r="G205" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H205" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I205" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J205" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="206" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B206">
         <v>53</v>
       </c>
       <c r="C206" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D206">
         <v>3666138</v>
@@ -7731,30 +7747,30 @@
         <v>61.78</v>
       </c>
       <c r="F206">
-        <v>19.4</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="G206" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H206" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I206" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J206" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="207" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B207">
         <v>19</v>
       </c>
       <c r="C207" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D207">
         <v>1354541</v>
@@ -7766,27 +7782,27 @@
         <v>6.73</v>
       </c>
       <c r="G207" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H207" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I207" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J207" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="208" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B208">
         <v>41</v>
       </c>
       <c r="C208" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D208">
         <v>1781754</v>
@@ -7798,27 +7814,27 @@
         <v>9.32</v>
       </c>
       <c r="G208" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H208" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I208" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J208" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="209" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B209">
         <v>29</v>
       </c>
       <c r="C209" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D209">
         <v>1641977</v>
@@ -7830,59 +7846,59 @@
         <v>6.55</v>
       </c>
       <c r="G209" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H209" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I209" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J209" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="210" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B210">
         <v>52</v>
       </c>
       <c r="C210" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D210">
         <v>1500569</v>
       </c>
       <c r="E210">
-        <v>76.51000000000001</v>
+        <v>76.510000000000005</v>
       </c>
       <c r="F210">
         <v>3.58</v>
       </c>
       <c r="G210" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H210" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I210" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J210" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="211" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B211">
         <v>36</v>
       </c>
       <c r="C211" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D211">
         <v>2199228</v>
@@ -7891,94 +7907,94 @@
         <v>77.28</v>
       </c>
       <c r="F211">
-        <v>17.4</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="G211" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H211" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I211" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J211" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="212" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B212">
         <v>46</v>
       </c>
       <c r="C212" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D212">
         <v>1729145</v>
       </c>
       <c r="E212">
-        <v>92.18000000000001</v>
+        <v>92.18</v>
       </c>
       <c r="F212">
-        <v>4.81</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="G212" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H212" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I212" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J212" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="213" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B213">
         <v>57</v>
       </c>
       <c r="C213" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D213">
         <v>1260435</v>
       </c>
       <c r="E213">
-        <v>85.59999999999999</v>
+        <v>85.6</v>
       </c>
       <c r="F213">
         <v>11.89</v>
       </c>
       <c r="G213" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H213" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I213" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J213" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="214" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B214">
         <v>55</v>
       </c>
       <c r="C214" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D214">
         <v>3700968</v>
@@ -7990,27 +8006,27 @@
         <v>5.74</v>
       </c>
       <c r="G214" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H214" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I214" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J214" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="215" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B215">
         <v>41</v>
       </c>
       <c r="C215" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D215">
         <v>3281190</v>
@@ -8022,27 +8038,27 @@
         <v>14.78</v>
       </c>
       <c r="G215" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H215" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I215" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J215" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="216" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B216">
         <v>11</v>
       </c>
       <c r="C216" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D216">
         <v>1470298</v>
@@ -8051,30 +8067,30 @@
         <v>87.13</v>
       </c>
       <c r="F216">
-        <v>9.279999999999999</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="G216" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H216" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I216" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J216" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="217" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B217">
         <v>30</v>
       </c>
       <c r="C217" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D217">
         <v>1254232</v>
@@ -8086,27 +8102,27 @@
         <v>10.95</v>
       </c>
       <c r="G217" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H217" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I217" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J217" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="218" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B218">
         <v>55</v>
       </c>
       <c r="C218" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D218">
         <v>2078963</v>
@@ -8118,27 +8134,27 @@
         <v>8.34</v>
       </c>
       <c r="G218" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H218" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I218" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J218" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="219" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B219">
         <v>46</v>
       </c>
       <c r="C219" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D219">
         <v>2536450</v>
@@ -8150,27 +8166,27 @@
         <v>13.43</v>
       </c>
       <c r="G219" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H219" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I219" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J219" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="220" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B220">
         <v>51</v>
       </c>
       <c r="C220" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D220">
         <v>2562991</v>
@@ -8182,27 +8198,27 @@
         <v>16.66</v>
       </c>
       <c r="G220" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H220" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I220" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J220" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="221" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B221">
         <v>6</v>
       </c>
       <c r="C221" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D221">
         <v>2230287</v>
@@ -8214,27 +8230,27 @@
         <v>15.04</v>
       </c>
       <c r="G221" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H221" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I221" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J221" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="222" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B222">
         <v>22</v>
       </c>
       <c r="C222" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D222">
         <v>4428426</v>
@@ -8246,27 +8262,27 @@
         <v>17.41</v>
       </c>
       <c r="G222" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H222" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I222" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J222" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="223" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B223">
         <v>17</v>
       </c>
       <c r="C223" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D223">
         <v>3657512</v>
@@ -8275,30 +8291,30 @@
         <v>81.64</v>
       </c>
       <c r="F223">
-        <v>18.49</v>
+        <v>18.489999999999998</v>
       </c>
       <c r="G223" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H223" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I223" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J223" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="224" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B224">
         <v>55</v>
       </c>
       <c r="C224" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D224">
         <v>3344946</v>
@@ -8307,30 +8323,30 @@
         <v>72.81</v>
       </c>
       <c r="F224">
-        <v>4.65</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="G224" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H224" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I224" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J224" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="225" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B225">
         <v>32</v>
       </c>
       <c r="C225" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D225">
         <v>2277267</v>
@@ -8342,27 +8358,27 @@
         <v>14.65</v>
       </c>
       <c r="G225" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H225" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I225" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J225" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="226" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B226">
         <v>49</v>
       </c>
       <c r="C226" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D226">
         <v>4298677</v>
@@ -8374,27 +8390,27 @@
         <v>18.47</v>
       </c>
       <c r="G226" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H226" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I226" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J226" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="227" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B227">
         <v>9</v>
       </c>
       <c r="C227" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D227">
         <v>3161552</v>
@@ -8403,62 +8419,62 @@
         <v>92.73</v>
       </c>
       <c r="F227">
-        <v>10.03</v>
+        <v>10.029999999999999</v>
       </c>
       <c r="G227" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H227" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I227" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J227" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="228" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B228">
         <v>23</v>
       </c>
       <c r="C228" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D228">
         <v>1650392</v>
       </c>
       <c r="E228">
-        <v>71.40000000000001</v>
+        <v>71.400000000000006</v>
       </c>
       <c r="F228">
         <v>14.13</v>
       </c>
       <c r="G228" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H228" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I228" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J228" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="229" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B229">
         <v>52</v>
       </c>
       <c r="C229" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D229">
         <v>1792185</v>
@@ -8470,59 +8486,59 @@
         <v>3.83</v>
       </c>
       <c r="G229" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H229" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I229" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J229" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="230" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B230">
         <v>57</v>
       </c>
       <c r="C230" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D230">
         <v>3965773</v>
       </c>
       <c r="E230">
-        <v>64.18000000000001</v>
+        <v>64.180000000000007</v>
       </c>
       <c r="F230">
         <v>15.92</v>
       </c>
       <c r="G230" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H230" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I230" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J230" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="231" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B231">
         <v>6</v>
       </c>
       <c r="C231" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D231">
         <v>2637784</v>
@@ -8534,27 +8550,27 @@
         <v>5.35</v>
       </c>
       <c r="G231" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H231" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I231" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J231" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="232" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B232">
         <v>27</v>
       </c>
       <c r="C232" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D232">
         <v>1296860</v>
@@ -8566,27 +8582,27 @@
         <v>6.75</v>
       </c>
       <c r="G232" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H232" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I232" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J232" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="233" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B233">
         <v>58</v>
       </c>
       <c r="C233" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D233">
         <v>3074033</v>
@@ -8598,59 +8614,59 @@
         <v>8.49</v>
       </c>
       <c r="G233" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H233" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I233" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J233" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="234" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B234">
         <v>48</v>
       </c>
       <c r="C234" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D234">
         <v>2496806</v>
       </c>
       <c r="E234">
-        <v>79.15000000000001</v>
+        <v>79.150000000000006</v>
       </c>
       <c r="F234">
         <v>15.81</v>
       </c>
       <c r="G234" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H234" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I234" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J234" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="235" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B235">
         <v>31</v>
       </c>
       <c r="C235" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D235">
         <v>3669399</v>
@@ -8662,59 +8678,59 @@
         <v>5.47</v>
       </c>
       <c r="G235" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H235" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I235" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J235" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="236" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B236">
         <v>19</v>
       </c>
       <c r="C236" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D236">
         <v>3419691</v>
       </c>
       <c r="E236">
-        <v>98.29000000000001</v>
+        <v>98.29</v>
       </c>
       <c r="F236">
         <v>7.99</v>
       </c>
       <c r="G236" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H236" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I236" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J236" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="237" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B237">
         <v>27</v>
       </c>
       <c r="C237" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D237">
         <v>2111282</v>
@@ -8726,59 +8742,59 @@
         <v>11.53</v>
       </c>
       <c r="G237" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H237" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I237" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J237" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="238" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B238">
         <v>18</v>
       </c>
       <c r="C238" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D238">
         <v>3531045</v>
       </c>
       <c r="E238">
-        <v>79.29000000000001</v>
+        <v>79.290000000000006</v>
       </c>
       <c r="F238">
         <v>14.44</v>
       </c>
       <c r="G238" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H238" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I238" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J238" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="239" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B239">
         <v>22</v>
       </c>
       <c r="C239" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D239">
         <v>2977548</v>
@@ -8790,27 +8806,27 @@
         <v>12.18</v>
       </c>
       <c r="G239" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H239" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I239" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J239" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="240" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B240">
         <v>27</v>
       </c>
       <c r="C240" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D240">
         <v>4674693</v>
@@ -8822,27 +8838,27 @@
         <v>10.45</v>
       </c>
       <c r="G240" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H240" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I240" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J240" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="241" spans="1:10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B241">
         <v>29</v>
       </c>
       <c r="C241" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D241">
         <v>4597073</v>
@@ -8854,91 +8870,91 @@
         <v>15.07</v>
       </c>
       <c r="G241" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H241" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I241" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J241" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="242" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B242">
         <v>49</v>
       </c>
       <c r="C242" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D242">
         <v>1624041</v>
       </c>
       <c r="E242">
-        <v>69.51000000000001</v>
+        <v>69.510000000000005</v>
       </c>
       <c r="F242">
-        <v>17.56</v>
+        <v>17.559999999999999</v>
       </c>
       <c r="G242" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H242" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I242" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J242" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="243" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B243">
         <v>36</v>
       </c>
       <c r="C243" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D243">
         <v>3038594</v>
       </c>
       <c r="E243">
-        <v>98.98999999999999</v>
+        <v>98.99</v>
       </c>
       <c r="F243">
         <v>18.05</v>
       </c>
       <c r="G243" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H243" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I243" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J243" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="244" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B244">
         <v>15</v>
       </c>
       <c r="C244" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D244">
         <v>3564629</v>
@@ -8950,27 +8966,27 @@
         <v>14.46</v>
       </c>
       <c r="G244" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H244" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I244" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J244" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="245" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B245">
         <v>42</v>
       </c>
       <c r="C245" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D245">
         <v>1145892</v>
@@ -8982,24 +8998,24 @@
         <v>14.29</v>
       </c>
       <c r="G245" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H245" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I245" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J245" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="246" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B246">
         <v>19</v>
       </c>
       <c r="C246" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D246">
         <v>4812315</v>
@@ -9008,19 +9024,19 @@
         <v>93.12</v>
       </c>
       <c r="F246">
-        <v>19.35</v>
+        <v>19.350000000000001</v>
       </c>
       <c r="G246" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H246" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I246" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J246" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
